--- a/case_studies/BOM_Balpremi_School_Independent.xlsx
+++ b/case_studies/BOM_Balpremi_School_Independent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\documents pc\My Research Work\Journal Paper\Done\LLM in WBLCA(09-20 to )\Journal_correction\github\LLM-Assisted-LCA-main\LLM-Assisted-LCA-main\case_studies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\documents pc\My Research Work\Journal Paper\Done\LLM in WBLCA(09-20 to )\Journal_correction\github\after_dummy_revised\LLM-Assisted-LCA-main\LLM-Assisted-LCA-main\case_studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D259C074-A59C-459C-AD91-226EE1938392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B259628D-5956-49D4-B29E-8E25CB25FB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="612" yWindow="-108" windowWidth="22536" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,10 +503,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="2">
-        <v>108253</v>
+        <v>108.253</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2">
         <v>1000</v>
